--- a/Quan Trac Lun/Data/HD XL01/KM0+500.xlsx
+++ b/Quan Trac Lun/Data/HD XL01/KM0+500.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Vba\bketech\Quan Trac Lun\Data\HD XL01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B22C7E04-03DF-4103-9BBF-762F351E56B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFE44700-1151-4D71-8B54-87C3F5F03114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{2C402617-1403-418F-9928-C6EF4DD57BF2}"/>
+    <workbookView xWindow="-8325" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{2C402617-1403-418F-9928-C6EF4DD57BF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -648,6 +648,11 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -655,18 +660,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -723,8 +716,15 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1073,139 +1073,139 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="32.450000000000003" customHeight="1">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="30"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="30"/>
-      <c r="AA1" s="30"/>
-      <c r="AB1" s="31"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="29"/>
+      <c r="AA1" s="29"/>
+      <c r="AB1" s="30"/>
     </row>
     <row r="2" spans="1:28" ht="17.25">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
-      <c r="T2" s="33"/>
-      <c r="U2" s="33"/>
-      <c r="V2" s="33"/>
-      <c r="W2" s="33"/>
-      <c r="X2" s="33"/>
-      <c r="Y2" s="33"/>
-      <c r="Z2" s="33"/>
-      <c r="AA2" s="33"/>
-      <c r="AB2" s="34"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="T2" s="32"/>
+      <c r="U2" s="32"/>
+      <c r="V2" s="32"/>
+      <c r="W2" s="32"/>
+      <c r="X2" s="32"/>
+      <c r="Y2" s="32"/>
+      <c r="Z2" s="32"/>
+      <c r="AA2" s="32"/>
+      <c r="AB2" s="33"/>
     </row>
     <row r="3" spans="1:28" ht="17.25">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="33"/>
-      <c r="L3" s="33"/>
-      <c r="M3" s="33"/>
-      <c r="N3" s="33"/>
-      <c r="O3" s="33"/>
-      <c r="P3" s="33"/>
-      <c r="Q3" s="33"/>
-      <c r="R3" s="33"/>
-      <c r="S3" s="33"/>
-      <c r="T3" s="33"/>
-      <c r="U3" s="33"/>
-      <c r="V3" s="33"/>
-      <c r="W3" s="33"/>
-      <c r="X3" s="33"/>
-      <c r="Y3" s="33"/>
-      <c r="Z3" s="33"/>
-      <c r="AA3" s="33"/>
-      <c r="AB3" s="34"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="32"/>
+      <c r="N3" s="32"/>
+      <c r="O3" s="32"/>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="32"/>
+      <c r="R3" s="32"/>
+      <c r="S3" s="32"/>
+      <c r="T3" s="32"/>
+      <c r="U3" s="32"/>
+      <c r="V3" s="32"/>
+      <c r="W3" s="32"/>
+      <c r="X3" s="32"/>
+      <c r="Y3" s="32"/>
+      <c r="Z3" s="32"/>
+      <c r="AA3" s="32"/>
+      <c r="AB3" s="33"/>
     </row>
     <row r="4" spans="1:28" ht="17.25">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
-      <c r="L4" s="36"/>
-      <c r="M4" s="36"/>
-      <c r="N4" s="36"/>
-      <c r="O4" s="36"/>
-      <c r="P4" s="36"/>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="36"/>
-      <c r="S4" s="36"/>
-      <c r="T4" s="36"/>
-      <c r="U4" s="36"/>
-      <c r="V4" s="36"/>
-      <c r="W4" s="36"/>
-      <c r="X4" s="36"/>
-      <c r="Y4" s="36"/>
-      <c r="Z4" s="36"/>
-      <c r="AA4" s="36"/>
-      <c r="AB4" s="37"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="35"/>
+      <c r="N4" s="35"/>
+      <c r="O4" s="35"/>
+      <c r="P4" s="35"/>
+      <c r="Q4" s="35"/>
+      <c r="R4" s="35"/>
+      <c r="S4" s="35"/>
+      <c r="T4" s="35"/>
+      <c r="U4" s="35"/>
+      <c r="V4" s="35"/>
+      <c r="W4" s="35"/>
+      <c r="X4" s="35"/>
+      <c r="Y4" s="35"/>
+      <c r="Z4" s="35"/>
+      <c r="AA4" s="35"/>
+      <c r="AB4" s="36"/>
     </row>
     <row r="5" spans="1:28">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -1235,11 +1235,11 @@
       <c r="AB5" s="4"/>
     </row>
     <row r="6" spans="1:28">
-      <c r="A6" s="40" t="s">
+      <c r="A6" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -1271,13 +1271,13 @@
       <c r="AB6" s="9"/>
     </row>
     <row r="7" spans="1:28">
-      <c r="A7" s="42" t="s">
+      <c r="A7" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="43"/>
+      <c r="C7" s="42"/>
       <c r="D7" s="10" t="s">
         <v>34</v>
       </c>
@@ -1311,71 +1311,71 @@
       <c r="AB7" s="13"/>
     </row>
     <row r="8" spans="1:28" ht="13.9" customHeight="1">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="43" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="21"/>
-      <c r="C8" s="44" t="s">
+      <c r="C8" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="44" t="s">
+      <c r="D8" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="28" t="s">
+      <c r="E8" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="22" t="s">
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="22" t="s">
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="M8" s="23"/>
-      <c r="N8" s="24"/>
-      <c r="O8" s="22" t="s">
+      <c r="M8" s="26"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="24"/>
-      <c r="R8" s="25" t="s">
+      <c r="P8" s="26"/>
+      <c r="Q8" s="27"/>
+      <c r="R8" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="S8" s="26"/>
-      <c r="T8" s="27"/>
-      <c r="U8" s="25" t="s">
+      <c r="S8" s="48"/>
+      <c r="T8" s="47"/>
+      <c r="U8" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="V8" s="26"/>
-      <c r="W8" s="27"/>
-      <c r="X8" s="28" t="s">
+      <c r="V8" s="48"/>
+      <c r="W8" s="47"/>
+      <c r="X8" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="Y8" s="28" t="s">
+      <c r="Y8" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="Z8" s="28" t="s">
+      <c r="Z8" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="AA8" s="25" t="s">
+      <c r="AA8" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="AB8" s="27"/>
+      <c r="AB8" s="47"/>
     </row>
     <row r="9" spans="1:28" ht="30">
-      <c r="A9" s="45"/>
+      <c r="A9" s="44"/>
       <c r="B9" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="46"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="28"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="24"/>
       <c r="F9" s="14" t="s">
         <v>22</v>
       </c>
@@ -1430,9 +1430,9 @@
       <c r="W9" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="X9" s="28"/>
-      <c r="Y9" s="28"/>
-      <c r="Z9" s="28"/>
+      <c r="X9" s="24"/>
+      <c r="Y9" s="24"/>
+      <c r="Z9" s="24"/>
       <c r="AA9" s="14" t="s">
         <v>25</v>
       </c>
@@ -1440,8 +1440,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="30">
-      <c r="A10" s="46"/>
+    <row r="10" spans="1:28">
+      <c r="A10" s="45"/>
       <c r="B10" s="17" t="s">
         <v>30</v>
       </c>
@@ -1601,6 +1601,9 @@
       </c>
     </row>
     <row r="12" spans="1:28">
+      <c r="A12" s="1">
+        <v>2</v>
+      </c>
       <c r="B12" s="20" t="s">
         <v>36</v>
       </c>
@@ -1675,6 +1678,9 @@
       </c>
     </row>
     <row r="13" spans="1:28">
+      <c r="A13" s="1">
+        <v>3</v>
+      </c>
       <c r="B13" s="20" t="s">
         <v>37</v>
       </c>
@@ -1749,6 +1755,9 @@
       </c>
     </row>
     <row r="14" spans="1:28">
+      <c r="A14" s="1">
+        <v>4</v>
+      </c>
       <c r="B14" s="20" t="s">
         <v>38</v>
       </c>
@@ -1823,6 +1832,9 @@
       </c>
     </row>
     <row r="15" spans="1:28">
+      <c r="A15" s="1">
+        <v>5</v>
+      </c>
       <c r="B15" s="20" t="s">
         <v>39</v>
       </c>
@@ -1897,6 +1909,9 @@
       </c>
     </row>
     <row r="16" spans="1:28">
+      <c r="A16" s="1">
+        <v>6</v>
+      </c>
       <c r="B16" s="20" t="s">
         <v>40</v>
       </c>
@@ -1971,6 +1986,9 @@
       </c>
     </row>
     <row r="17" spans="1:26">
+      <c r="A17" s="1">
+        <v>7</v>
+      </c>
       <c r="B17" s="20" t="s">
         <v>41</v>
       </c>
@@ -2045,83 +2063,89 @@
       </c>
     </row>
     <row r="18" spans="1:26">
-      <c r="B18" s="47" t="s">
+      <c r="A18" s="1">
+        <v>8</v>
+      </c>
+      <c r="B18" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="48">
+      <c r="C18" s="23">
         <v>835</v>
       </c>
-      <c r="D18" s="48">
+      <c r="D18" s="23">
         <v>2602</v>
       </c>
-      <c r="E18" s="48">
+      <c r="E18" s="23">
         <v>3437</v>
       </c>
-      <c r="F18" s="48">
+      <c r="F18" s="23">
         <v>-507</v>
       </c>
-      <c r="G18" s="48">
+      <c r="G18" s="23">
         <v>-513</v>
       </c>
-      <c r="H18" s="48">
+      <c r="H18" s="23">
         <v>-510</v>
       </c>
-      <c r="I18" s="48">
+      <c r="I18" s="23">
         <v>3944</v>
       </c>
-      <c r="J18" s="48">
+      <c r="J18" s="23">
         <v>3950</v>
       </c>
-      <c r="K18" s="48">
+      <c r="K18" s="23">
         <v>3947</v>
       </c>
-      <c r="L18" s="48">
-        <v>2000</v>
-      </c>
-      <c r="M18" s="48">
-        <v>2000</v>
-      </c>
-      <c r="N18" s="48">
-        <v>2000</v>
-      </c>
-      <c r="O18" s="48">
+      <c r="L18" s="23">
+        <v>2000</v>
+      </c>
+      <c r="M18" s="23">
+        <v>2000</v>
+      </c>
+      <c r="N18" s="23">
+        <v>2000</v>
+      </c>
+      <c r="O18" s="23">
         <v>1944</v>
       </c>
-      <c r="P18" s="48">
+      <c r="P18" s="23">
         <v>1950</v>
       </c>
-      <c r="Q18" s="48">
+      <c r="Q18" s="23">
         <v>1947</v>
       </c>
-      <c r="R18" s="48">
+      <c r="R18" s="23">
         <v>12</v>
       </c>
-      <c r="S18" s="48">
+      <c r="S18" s="23">
         <v>10</v>
       </c>
-      <c r="T18" s="48">
+      <c r="T18" s="23">
         <v>11</v>
       </c>
-      <c r="U18" s="48">
+      <c r="U18" s="23">
         <v>-56</v>
       </c>
-      <c r="V18" s="48">
+      <c r="V18" s="23">
         <v>-50</v>
       </c>
-      <c r="W18" s="48">
+      <c r="W18" s="23">
         <v>-53</v>
       </c>
-      <c r="X18" s="48">
+      <c r="X18" s="23">
         <v>1.4500000000000002</v>
       </c>
-      <c r="Y18" s="48">
+      <c r="Y18" s="23">
         <v>0.3</v>
       </c>
-      <c r="Z18" s="48">
+      <c r="Z18" s="23">
         <v>0.3</v>
       </c>
     </row>
     <row r="19" spans="1:26">
+      <c r="A19" s="1">
+        <v>9</v>
+      </c>
       <c r="B19" s="20" t="s">
         <v>43</v>
       </c>
@@ -2196,6 +2220,9 @@
       </c>
     </row>
     <row r="20" spans="1:26">
+      <c r="A20" s="1">
+        <v>10</v>
+      </c>
       <c r="B20" s="20" t="s">
         <v>44</v>
       </c>
@@ -2270,6 +2297,9 @@
       </c>
     </row>
     <row r="21" spans="1:26">
+      <c r="A21" s="1">
+        <v>11</v>
+      </c>
       <c r="B21" s="20" t="s">
         <v>45</v>
       </c>
@@ -2344,6 +2374,9 @@
       </c>
     </row>
     <row r="22" spans="1:26">
+      <c r="A22" s="1">
+        <v>12</v>
+      </c>
       <c r="B22" s="20" t="s">
         <v>46</v>
       </c>
@@ -2418,6 +2451,9 @@
       </c>
     </row>
     <row r="23" spans="1:26">
+      <c r="A23" s="1">
+        <v>13</v>
+      </c>
       <c r="B23" s="20" t="s">
         <v>47</v>
       </c>
@@ -2492,6 +2528,9 @@
       </c>
     </row>
     <row r="24" spans="1:26">
+      <c r="A24" s="1">
+        <v>14</v>
+      </c>
       <c r="B24" s="20" t="s">
         <v>48</v>
       </c>
@@ -2566,6 +2605,9 @@
       </c>
     </row>
     <row r="25" spans="1:26">
+      <c r="A25" s="1">
+        <v>15</v>
+      </c>
       <c r="B25" s="20" t="s">
         <v>49</v>
       </c>
@@ -2640,6 +2682,9 @@
       </c>
     </row>
     <row r="26" spans="1:26">
+      <c r="A26" s="1">
+        <v>16</v>
+      </c>
       <c r="B26" s="20" t="s">
         <v>50</v>
       </c>
@@ -2714,84 +2759,89 @@
       </c>
     </row>
     <row r="27" spans="1:26">
-      <c r="A27" s="48"/>
-      <c r="B27" s="47" t="s">
+      <c r="A27" s="1">
+        <v>17</v>
+      </c>
+      <c r="B27" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="C27" s="48">
+      <c r="C27" s="23">
         <v>835</v>
       </c>
-      <c r="D27" s="48">
+      <c r="D27" s="23">
         <v>2012</v>
       </c>
-      <c r="E27" s="48">
+      <c r="E27" s="23">
         <v>2847</v>
       </c>
-      <c r="F27" s="48">
+      <c r="F27" s="23">
         <v>-1033</v>
       </c>
-      <c r="G27" s="48">
+      <c r="G27" s="23">
         <v>-1044</v>
       </c>
-      <c r="H27" s="48">
+      <c r="H27" s="23">
         <v>-1039</v>
       </c>
-      <c r="I27" s="48">
+      <c r="I27" s="23">
         <v>3880</v>
       </c>
-      <c r="J27" s="48">
+      <c r="J27" s="23">
         <v>3891</v>
       </c>
-      <c r="K27" s="48">
+      <c r="K27" s="23">
         <v>3886</v>
       </c>
-      <c r="L27" s="48">
-        <v>2000</v>
-      </c>
-      <c r="M27" s="48">
-        <v>2000</v>
-      </c>
-      <c r="N27" s="48">
-        <v>2000</v>
-      </c>
-      <c r="O27" s="48">
+      <c r="L27" s="23">
+        <v>2000</v>
+      </c>
+      <c r="M27" s="23">
+        <v>2000</v>
+      </c>
+      <c r="N27" s="23">
+        <v>2000</v>
+      </c>
+      <c r="O27" s="23">
         <v>1880</v>
       </c>
-      <c r="P27" s="48">
+      <c r="P27" s="23">
         <v>1891</v>
       </c>
-      <c r="Q27" s="48">
+      <c r="Q27" s="23">
         <v>1886</v>
       </c>
-      <c r="R27" s="48">
+      <c r="R27" s="23">
         <v>10</v>
       </c>
-      <c r="S27" s="48">
+      <c r="S27" s="23">
         <v>9</v>
       </c>
-      <c r="T27" s="48">
+      <c r="T27" s="23">
         <v>9</v>
       </c>
-      <c r="U27" s="48">
+      <c r="U27" s="23">
         <v>-120</v>
       </c>
-      <c r="V27" s="48">
+      <c r="V27" s="23">
         <v>-109</v>
       </c>
-      <c r="W27" s="48">
+      <c r="W27" s="23">
         <v>-114</v>
       </c>
-      <c r="X27" s="48">
+      <c r="X27" s="23">
         <v>1.6910000000000007</v>
       </c>
-      <c r="Y27" s="48">
+      <c r="Y27" s="23">
         <v>0.3</v>
       </c>
-      <c r="Z27" s="48">
+      <c r="Z27" s="23">
         <v>0.6</v>
       </c>
     </row>
     <row r="28" spans="1:26">
+      <c r="A28" s="1">
+        <v>18</v>
+      </c>
       <c r="B28" s="20" t="s">
         <v>52</v>
       </c>
@@ -2866,6 +2916,9 @@
       </c>
     </row>
     <row r="29" spans="1:26">
+      <c r="A29" s="1">
+        <v>19</v>
+      </c>
       <c r="B29" s="20" t="s">
         <v>53</v>
       </c>
@@ -2940,6 +2993,9 @@
       </c>
     </row>
     <row r="30" spans="1:26">
+      <c r="A30" s="1">
+        <v>20</v>
+      </c>
       <c r="B30" s="20" t="s">
         <v>54</v>
       </c>
@@ -3014,6 +3070,9 @@
       </c>
     </row>
     <row r="31" spans="1:26">
+      <c r="A31" s="1">
+        <v>21</v>
+      </c>
       <c r="B31" s="20" t="s">
         <v>55</v>
       </c>
@@ -3088,6 +3147,9 @@
       </c>
     </row>
     <row r="32" spans="1:26">
+      <c r="A32" s="1">
+        <v>22</v>
+      </c>
       <c r="B32" s="20" t="s">
         <v>56</v>
       </c>
@@ -3161,7 +3223,10 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="33" spans="2:26">
+    <row r="33" spans="1:26">
+      <c r="A33" s="1">
+        <v>23</v>
+      </c>
       <c r="B33" s="20" t="s">
         <v>57</v>
       </c>
@@ -3235,7 +3300,10 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="34" spans="2:26">
+    <row r="34" spans="1:26">
+      <c r="A34" s="1">
+        <v>24</v>
+      </c>
       <c r="B34" s="20" t="s">
         <v>58</v>
       </c>
@@ -3309,7 +3377,10 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="35" spans="2:26">
+    <row r="35" spans="1:26">
+      <c r="A35" s="1">
+        <v>25</v>
+      </c>
       <c r="B35" s="20" t="s">
         <v>59</v>
       </c>
@@ -3383,7 +3454,10 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="36" spans="2:26">
+    <row r="36" spans="1:26">
+      <c r="A36" s="1">
+        <v>26</v>
+      </c>
       <c r="B36" s="20" t="s">
         <v>60</v>
       </c>
@@ -3457,7 +3531,10 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="37" spans="2:26">
+    <row r="37" spans="1:26">
+      <c r="A37" s="1">
+        <v>27</v>
+      </c>
       <c r="B37" s="20" t="s">
         <v>61</v>
       </c>
@@ -3531,7 +3608,10 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="38" spans="2:26">
+    <row r="38" spans="1:26">
+      <c r="A38" s="1">
+        <v>28</v>
+      </c>
       <c r="B38" s="20" t="s">
         <v>62</v>
       </c>
@@ -3605,7 +3685,10 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="39" spans="2:26">
+    <row r="39" spans="1:26">
+      <c r="A39" s="1">
+        <v>29</v>
+      </c>
       <c r="B39" s="20" t="s">
         <v>63</v>
       </c>
@@ -3679,7 +3762,10 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="40" spans="2:26">
+    <row r="40" spans="1:26">
+      <c r="A40" s="1">
+        <v>30</v>
+      </c>
       <c r="B40" s="20" t="s">
         <v>64</v>
       </c>
@@ -3753,7 +3839,10 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="41" spans="2:26">
+    <row r="41" spans="1:26">
+      <c r="A41" s="1">
+        <v>31</v>
+      </c>
       <c r="B41" s="20" t="s">
         <v>65</v>
       </c>
@@ -3829,6 +3918,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="O8:Q8"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="U8:W8"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="I8:K8"/>
@@ -3845,11 +3939,6 @@
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="AA8:AB8"/>
     <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="O8:Q8"/>
-    <mergeCell ref="R8:T8"/>
-    <mergeCell ref="U8:W8"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
   </mergeCells>
   <pageMargins left="0.19685039370078741" right="7.874015748031496E-2" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="53" fitToHeight="0" orientation="landscape" r:id="rId1"/>

--- a/Quan Trac Lun/Data/HD XL01/KM0+500.xlsx
+++ b/Quan Trac Lun/Data/HD XL01/KM0+500.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Vba\bketech\Quan Trac Lun\Data\HD XL01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VBA Project\bketech\Quan Trac Lun\Data\HD XL01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFE44700-1151-4D71-8B54-87C3F5F03114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68AC9C09-974D-4C34-91CF-B6EE8A5CBC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-8325" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{2C402617-1403-418F-9928-C6EF4DD57BF2}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2C402617-1403-418F-9928-C6EF4DD57BF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -245,7 +245,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -263,14 +263,14 @@
       <b/>
       <sz val="13"/>
       <color theme="1"/>
-      <name val="Aptos Display"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Display"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -279,7 +279,7 @@
       <u/>
       <sz val="13"/>
       <color theme="1"/>
-      <name val="Aptos Display"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -287,20 +287,20 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Display"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Aptos Display"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Aptos Display"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -1065,14 +1065,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB41"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.85546875" style="1"/>
+    <col min="1" max="1" width="3.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.8984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="32.450000000000003" customHeight="1">
+    <row r="1" spans="1:28" ht="32.4" customHeight="1">
       <c r="A1" s="28" t="s">
         <v>31</v>
       </c>
@@ -1104,7 +1104,7 @@
       <c r="AA1" s="29"/>
       <c r="AB1" s="30"/>
     </row>
-    <row r="2" spans="1:28" ht="17.25">
+    <row r="2" spans="1:28" ht="16.8">
       <c r="A2" s="31" t="s">
         <v>32</v>
       </c>
@@ -1136,7 +1136,7 @@
       <c r="AA2" s="32"/>
       <c r="AB2" s="33"/>
     </row>
-    <row r="3" spans="1:28" ht="17.25">
+    <row r="3" spans="1:28" ht="16.8">
       <c r="A3" s="31" t="s">
         <v>33</v>
       </c>
@@ -1168,7 +1168,7 @@
       <c r="AA3" s="32"/>
       <c r="AB3" s="33"/>
     </row>
-    <row r="4" spans="1:28" ht="17.25">
+    <row r="4" spans="1:28" ht="16.8">
       <c r="A4" s="34" t="s">
         <v>0</v>
       </c>
@@ -1310,7 +1310,7 @@
       <c r="AA7" s="10"/>
       <c r="AB7" s="13"/>
     </row>
-    <row r="8" spans="1:28" ht="13.9" customHeight="1">
+    <row r="8" spans="1:28" ht="13.95" customHeight="1">
       <c r="A8" s="43" t="s">
         <v>8</v>
       </c>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AB8" s="47"/>
     </row>
-    <row r="9" spans="1:28" ht="30">
+    <row r="9" spans="1:28">
       <c r="A9" s="44"/>
       <c r="B9" s="15" t="s">
         <v>29</v>

--- a/Quan Trac Lun/Data/HD XL01/KM0+500.xlsx
+++ b/Quan Trac Lun/Data/HD XL01/KM0+500.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VBA Project\bketech\Quan Trac Lun\Data\HD XL01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Vba\bketech\Quan Trac Lun\Data\HD XL01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68AC9C09-974D-4C34-91CF-B6EE8A5CBC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35B93291-4AD9-422A-B7E8-792D8DDCFCC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2C402617-1403-418F-9928-C6EF4DD57BF2}"/>
+    <workbookView xWindow="-8325" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{2C402617-1403-418F-9928-C6EF4DD57BF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -245,7 +245,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -263,14 +263,14 @@
       <b/>
       <sz val="13"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Aptos Display"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Aptos Display"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -279,7 +279,7 @@
       <u/>
       <sz val="13"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Aptos Display"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -287,20 +287,20 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Aptos Display"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Times New Roman"/>
+      <name val="Aptos Display"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Times New Roman"/>
+      <name val="Aptos Display"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -1065,14 +1065,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB41"/>
-  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.8984375" style="1"/>
+    <col min="1" max="1" width="3.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="32.4" customHeight="1">
+    <row r="1" spans="1:28" ht="32.450000000000003" customHeight="1">
       <c r="A1" s="28" t="s">
         <v>31</v>
       </c>
@@ -1104,7 +1104,7 @@
       <c r="AA1" s="29"/>
       <c r="AB1" s="30"/>
     </row>
-    <row r="2" spans="1:28" ht="16.8">
+    <row r="2" spans="1:28" ht="17.25">
       <c r="A2" s="31" t="s">
         <v>32</v>
       </c>
@@ -1136,7 +1136,7 @@
       <c r="AA2" s="32"/>
       <c r="AB2" s="33"/>
     </row>
-    <row r="3" spans="1:28" ht="16.8">
+    <row r="3" spans="1:28" ht="17.25">
       <c r="A3" s="31" t="s">
         <v>33</v>
       </c>
@@ -1168,7 +1168,7 @@
       <c r="AA3" s="32"/>
       <c r="AB3" s="33"/>
     </row>
-    <row r="4" spans="1:28" ht="16.8">
+    <row r="4" spans="1:28" ht="17.25">
       <c r="A4" s="34" t="s">
         <v>0</v>
       </c>
@@ -1310,7 +1310,7 @@
       <c r="AA7" s="10"/>
       <c r="AB7" s="13"/>
     </row>
-    <row r="8" spans="1:28" ht="13.95" customHeight="1">
+    <row r="8" spans="1:28" ht="13.9" customHeight="1">
       <c r="A8" s="43" t="s">
         <v>8</v>
       </c>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AB8" s="47"/>
     </row>
-    <row r="9" spans="1:28">
+    <row r="9" spans="1:28" ht="30">
       <c r="A9" s="44"/>
       <c r="B9" s="15" t="s">
         <v>29</v>
@@ -1570,7 +1570,7 @@
         <v>4000</v>
       </c>
       <c r="Q11" s="1">
-        <v>400</v>
+        <v>4000</v>
       </c>
       <c r="R11" s="1">
         <v>0</v>
